--- a/PDF/data/eventos.xlsx
+++ b/PDF/data/eventos.xlsx
@@ -1,85 +1,105 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\monic\Documents\HV\PDF\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{504DF9D1-BCFC-4827-A784-9D481539CA5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
   <si>
-    <t>what</t>
-  </si>
-  <si>
-    <t>when</t>
-  </si>
-  <si>
-    <t>with</t>
-  </si>
-  <si>
-    <t>where</t>
-  </si>
-  <si>
-    <t>why</t>
-  </si>
-  <si>
-    <t>Organizadora</t>
-  </si>
-  <si>
-    <t>Respondiendo a las injusticias epistemicas</t>
-  </si>
-  <si>
-    <t>Universidad Central</t>
-  </si>
-  <si>
-    <t>Para nosotras, pero con nosotras</t>
-  </si>
-  <si>
-    <t>Estigmas y reparaciones, retos para las victimas de violencia sexual en
+    <t xml:space="preserve">what</t>
+  </si>
+  <si>
+    <t xml:space="preserve">when</t>
+  </si>
+  <si>
+    <t xml:space="preserve">with</t>
+  </si>
+  <si>
+    <t xml:space="preserve">where</t>
+  </si>
+  <si>
+    <t xml:space="preserve">why</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Organizadora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Respondiendo a las injusticias epistemicas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Universidad Central</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Para nosotras, pero con nosotras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estigmas y reparaciones, retos para las victimas de violencia sexual en
 conflictos armados</t>
   </si>
   <si>
-    <t>Proyecto Tumaco</t>
-  </si>
-  <si>
-    <t>Lanzamiento del observatorio de Género y No es Hora
-de Calla</t>
-  </si>
-  <si>
-    <t>Hablemos de diversidad, género y nuevas tecnologias</t>
+    <t xml:space="preserve">Proyecto Tumaco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lanzamiento del observatorio de Género y No es Hora
+de Callar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hablemos de diversidad, género y nuevas tecnologias</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
-      <u/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <u val="single"/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -91,7 +111,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -99,88 +119,178 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+  <cellStyleXfs count="21">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+  <cellXfs count="4">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+  <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="*unknown*" xfId="20" builtinId="8"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0563C1"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="44546a"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="e7e6e6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4472c4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="ed7d31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="a5a5a5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="ffc000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="5b9bd5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="70ad47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0563c1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="954f72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Calibri Light" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -190,39 +300,35 @@
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -230,64 +336,37 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -297,7 +376,6 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
-            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:gradFill>
@@ -305,7 +383,6 @@
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -313,7 +390,6 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -321,125 +397,131 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
-                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:E10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.4453125" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="34.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="75.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="61.88671875" customWidth="1"/>
-    <col min="5" max="5" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="5.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="75.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="61.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="4.33"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="0" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="0" t="n">
         <v>2020</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="0" t="s">
         <v>7</v>
       </c>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="0" t="n">
         <v>2020</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="0" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="4" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="0" t="n">
         <v>2019</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="0" t="n">
         <v>2018</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="0" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="6" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="0" t="n">
         <v>2017</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="0" t="n">
         <v>2017</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="0" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E10" s="2"/>
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E10" s="3"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="90" verticalDpi="90"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>